--- a/exports/colleges/9127_symbiosis-law-school-sls-pune.xlsx
+++ b/exports/colleges/9127_symbiosis-law-school-sls-pune.xlsx
@@ -605,11 +605,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="69" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -692,7 +692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LLB</t>
+          <t>Bachelor of Law [L.L.B]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bachelor of Law [L.L.B]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.37 Lakhs</t>
+          <t>10.37 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Graduation with 45% + AIAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AICLET</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Sept - 30 Nov 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.5 Lakhs</t>
+          <t>25.5 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with 45% + SLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Sept - 30 Nov 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Master of Laws [L.L.M]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.8 Lakhs</t>
+          <t>2.8 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.L.B. + AIAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AILET</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>7 Aug - 10 Nov 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.5 Lakhs</t>
+          <t>25.5 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10+2 with 45% + SLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SLAT</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Sept - 30 Nov 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Graduate Diploma in Law</t>
+          <t>Diploma in International Business Laws And Corporate Laws In India</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Diploma in International Business Laws And Corporate Laws In India</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10+2</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>LLB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Bachelor of Law [L.L.B]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Bachelor of Law [L.L.B]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.30 lakh</t>
+          <t>10.37 Lakhs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 45% + AIAT</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>AICLET</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Bachelor of Business Administration [BBA] + Bachelor of Laws [L.L.B.] {Hons.}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Bachelor of Business Administration [BBA] + Bachelor of Laws [L.L.B.] {Hons.}</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.25 Lakhs</t>
+          <t>25.5 Lakhs</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 45% + SLAT</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>SLAT</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.17 Lakhs</t>
+          <t>2.8 Lakhs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>L.L.B. + AIAT</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>AILET</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.62 Lakhs</t>
+          <t>25.5 Lakhs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 45% + SLAT</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>SLAT</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Total Fees</t>
+          <t>Graduate Diploma in Law</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Total Fees</t>
+          <t>Diploma in International Business Laws And Corporate Laws In India</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Total Fees</t>
+          <t>Diploma in International Business Laws And Corporate Laws In India</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.25 Lakhs</t>
+          <t>35,500</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Criminal And Security Law</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Criminal And Security Law</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Criminal And Security Law</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.60 Lakhs</t>
+          <t>2.6 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>L.L.B. + AIAT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other Fee</t>
+          <t>Intellectual Property Rights And Technology Law</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other Fee</t>
+          <t>Intellectual Property Rights And Technology Law</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Other Fee</t>
+          <t>Intellectual Property Rights And Technology Law</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>2.6 Lakhs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>L.L.B. + AIAT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Constitutional Law And Administrative Law</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Constitutional Law And Administrative Law</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Constitutional Law And Administrative Law</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.70 Lakhs</t>
+          <t>2.6 Lakhs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>L.L.B. + AIAT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Criminal And Security Law</t>
+          <t>Family Law</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Criminal And Security Law</t>
+          <t>Family Law</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Criminal And Security Law</t>
+          <t>Family Law</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1560,17 +1560,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Intellectual Property Rights And Technology Law</t>
+          <t>Human Rights</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Intellectual Property Rights And Technology Law</t>
+          <t>Human Rights</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Intellectual Property Rights And Technology Law</t>
+          <t>Human Rights</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Constitutional Law And Administrative Law</t>
+          <t>Technology Law</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Constitutional Law And Administrative Law</t>
+          <t>Technology Law</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Constitutional Law And Administrative Law</t>
+          <t>Technology Law</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1684,17 +1684,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Family Law</t>
+          <t>Environmental Law, Energy &amp; Climate Change</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Family Law</t>
+          <t>Environmental Law, Energy &amp; Climate Change</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Family Law</t>
+          <t>Environmental Law, Energy &amp; Climate Change</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Human Rights</t>
+          <t>International Law</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Human Rights</t>
+          <t>International Law</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Human Rights</t>
+          <t>International Law</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1808,17 +1808,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Technology Law</t>
+          <t>Public Policy &amp; Governance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Technology Law</t>
+          <t>Public Policy &amp; Governance</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Technology Law</t>
+          <t>Public Policy &amp; Governance</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1870,22 +1870,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Environmental Law, Energy &amp; Climate Change</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Environmental Law, Energy &amp; Climate Change</t>
+          <t>Ph.D (General)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Environmental Law, Energy &amp; Climate Change</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.6 Lakhs</t>
+          <t>Post Graduation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.L.B. + AIAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>International Law</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>International Law</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>International Law</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.6 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.L.B. + AIAT</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1994,27 +1994,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Public Policy &amp; Governance</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Public Policy &amp; Governance</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Public Policy &amp; Governance</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.6 Lakhs</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.L.B. + AIAT</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2056,27 +2056,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Humanities And Social Science</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Humanities And Social Science</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2118,27 +2118,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Public Policy</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>3.4 Lakhs</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Postgraduation in relevant field</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2180,22 +2180,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>LL.B.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>LL.B.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>LL.B.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29000</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2242,27 +2242,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>BBA LL.B(Hons)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>BBA LL.B(Hons)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2304,27 +2304,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>LL.M</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ph.D (General)</t>
+          <t>LL.M</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>LL.M</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Post Graduation</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2366,27 +2366,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>BA.LL.B (Hons)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>BA.LL.B (Hons)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Doctorate</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2428,27 +2428,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ph.D</t>
+          <t>UG Diploma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>UG Diploma</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>UG Diploma</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.4 Lakhs</t>
+          <t>160</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Postgraduation in relevant field</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>GATE / UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2477,440 +2477,6 @@
         </is>
       </c>
       <c r="L30" t="inlineStr">
-        <is>
-          <t>Doctorate</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Ph.D</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Humanities And Social Science</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Humanities And Social Science</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>3.4 Lakhs</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3-5 Years</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Postgraduation in relevant field</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>GATE / UGC NET</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Doctorate</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Ph.D</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Public Policy</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Public Policy</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>3.4 Lakhs</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>3-5 Years</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Postgraduation in relevant field</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>GATE / UGC NET</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Doctorate</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>LL.B.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>LL.B.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>LL.B.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>BBA</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BBA LL.B(Hons)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>BBA LL.B(Hons)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3 Years</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>LL.M</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>LL.M</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LL.M</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>BA.LL.B (Hons)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>BA.LL.B (Hons)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3 Years</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>9127</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>UG Diploma</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>UG Diploma</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>UG Diploma</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1 Year</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
         <is>
           <t>PG</t>
         </is>
